--- a/crg_drawio/input/sub_clock_table.xlsx
+++ b/crg_drawio/input/sub_clock_table.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClockTree" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>OCC/SCAN MUX</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -474,15 +474,10 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CE_DISEN</t>
+          <t>ATTR</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>ATTR</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -504,13 +499,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
         <is>
           <t>test mode</t>
         </is>
@@ -532,13 +526,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>2000MHz</t>
         </is>
@@ -560,13 +553,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>internal</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,13 +576,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
         <is>
           <t>25MHz</t>
         </is>
@@ -614,7 +605,6 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -646,13 +636,12 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
         <is>
           <t>2000MHz</t>
         </is>
@@ -690,13 +679,12 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
         <is>
           <t>1000MHz</t>
         </is>
@@ -734,13 +722,12 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
         <is>
           <t>500MHz</t>
         </is>
@@ -766,13 +753,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
         <is>
           <t>500MHz</t>
         </is>
@@ -806,13 +792,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
         <is>
           <t>500MHz</t>
         </is>
@@ -846,13 +831,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
         <is>
           <t>500MHz</t>
         </is>
@@ -890,13 +874,12 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
-        <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -922,13 +905,12 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -962,13 +944,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1002,13 +983,12 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1034,13 +1014,12 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1074,13 +1053,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1114,13 +1092,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1154,13 +1131,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1194,13 +1170,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1234,13 +1209,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1286,13 +1260,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1326,13 +1299,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1378,13 +1350,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1418,13 +1389,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1470,13 +1440,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1510,13 +1479,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1562,13 +1530,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1602,13 +1569,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1654,13 +1620,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1694,13 +1659,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
@@ -1746,13 +1710,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
         <is>
           <t>667MHz</t>
         </is>
@@ -1786,13 +1749,12 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
         <is>
           <t>200MHz</t>
         </is>
